--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_steel.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_steel.xlsx
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="K2">
-        <v>-1.78</v>
+        <v>-1.69</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.958579881656805e-05</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.000591715976331361</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,34 +609,37 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.001</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.765</v>
+        <v>0.25</v>
       </c>
       <c r="V2">
-        <v>0.05</v>
+        <v>0.007396449704142012</v>
       </c>
       <c r="W2">
-        <v>-0.04659685863874345</v>
+        <v>-0.04366925064599483</v>
       </c>
       <c r="X2">
-        <v>0.1307504180660215</v>
+        <v>0.2173403983475114</v>
       </c>
       <c r="Y2">
-        <v>-0.1773472767047649</v>
+        <v>-0.2610096489935063</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.02669415371603763</v>
+        <v>-0.02741531567154343</v>
       </c>
       <c r="AB2">
-        <v>0.1307504180660215</v>
+        <v>0.2173403983475114</v>
       </c>
       <c r="AC2">
-        <v>-0.1574445717820591</v>
+        <v>-0.2447557140190549</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.765</v>
+        <v>-0.25</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -657,22 +660,16 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.05263157894736842</v>
+        <v>-0.00745156482861401</v>
       </c>
       <c r="AK2">
-        <v>-0.02016607354685646</v>
+        <v>-0.006747638326585695</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.001</v>
-      </c>
-      <c r="AO2">
-        <v>-1010</v>
-      </c>
-      <c r="AQ2">
-        <v>-1010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -692,16 +689,16 @@
         </is>
       </c>
       <c r="K3">
-        <v>-1.78</v>
+        <v>-1.69</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>2.958579881656805e-05</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.000591715976331361</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -713,34 +710,37 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.001</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.765</v>
+        <v>0.25</v>
       </c>
       <c r="V3">
-        <v>0.05</v>
+        <v>0.007396449704142012</v>
       </c>
       <c r="W3">
-        <v>-0.04659685863874345</v>
+        <v>-0.04366925064599483</v>
       </c>
       <c r="X3">
-        <v>0.1307504180660215</v>
+        <v>0.2173403983475114</v>
       </c>
       <c r="Y3">
-        <v>-0.1773472767047649</v>
+        <v>-0.2610096489935063</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.02669415371603763</v>
+        <v>-0.02741531567154343</v>
       </c>
       <c r="AB3">
-        <v>0.1307504180660215</v>
+        <v>0.2173403983475114</v>
       </c>
       <c r="AC3">
-        <v>-0.1574445717820591</v>
+        <v>-0.2447557140190549</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.765</v>
+        <v>-0.25</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -761,22 +761,16 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.05263157894736842</v>
+        <v>-0.00745156482861401</v>
       </c>
       <c r="AK3">
-        <v>-0.02016607354685646</v>
+        <v>-0.006747638326585695</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.001</v>
-      </c>
-      <c r="AO3">
-        <v>-1010</v>
-      </c>
-      <c r="AQ3">
-        <v>-1010</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_steel.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_steel.xlsx
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="K2">
-        <v>-1.69</v>
+        <v>8.27</v>
       </c>
       <c r="M2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.958579881656805e-05</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.000591715976331361</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,64 +606,61 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0.001</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0.25</v>
+        <v>0.573</v>
       </c>
       <c r="V2">
-        <v>0.007396449704142012</v>
+        <v>0.007431906614785992</v>
       </c>
       <c r="W2">
-        <v>-0.04366925064599483</v>
+        <v>0.22171581769437</v>
       </c>
       <c r="X2">
-        <v>0.2173403983475114</v>
+        <v>0.128129215324823</v>
       </c>
       <c r="Y2">
-        <v>-0.2610096489935063</v>
+        <v>0.09358660236954702</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.02741531567154343</v>
+        <v>-0.01819163292847504</v>
       </c>
       <c r="AB2">
-        <v>0.2173403983475114</v>
+        <v>0.1270296102028556</v>
       </c>
       <c r="AC2">
-        <v>-0.2447557140190549</v>
+        <v>-0.1452212431313306</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG2">
-        <v>-0.25</v>
+        <v>0.7270000000000001</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.01658163265306123</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.01508120649651972</v>
       </c>
       <c r="AJ2">
-        <v>-0.00745156482861401</v>
+        <v>0.009341231192259757</v>
       </c>
       <c r="AK2">
-        <v>-0.006747638326585695</v>
+        <v>0.008490312635033342</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -689,16 +686,16 @@
         </is>
       </c>
       <c r="K3">
-        <v>-1.69</v>
+        <v>8.27</v>
       </c>
       <c r="M3">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>2.958579881656805e-05</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.000591715976331361</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -707,64 +704,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.001</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.25</v>
+        <v>0.573</v>
       </c>
       <c r="V3">
-        <v>0.007396449704142012</v>
+        <v>0.007431906614785992</v>
       </c>
       <c r="W3">
-        <v>-0.04366925064599483</v>
+        <v>0.22171581769437</v>
       </c>
       <c r="X3">
-        <v>0.2173403983475114</v>
+        <v>0.128129215324823</v>
       </c>
       <c r="Y3">
-        <v>-0.2610096489935063</v>
+        <v>0.09358660236954702</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.02741531567154343</v>
+        <v>-0.01819163292847504</v>
       </c>
       <c r="AB3">
-        <v>0.2173403983475114</v>
+        <v>0.1270296102028556</v>
       </c>
       <c r="AC3">
-        <v>-0.2447557140190549</v>
+        <v>-0.1452212431313306</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG3">
-        <v>-0.25</v>
+        <v>0.7270000000000001</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.01658163265306123</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.01508120649651972</v>
       </c>
       <c r="AJ3">
-        <v>-0.00745156482861401</v>
+        <v>0.009341231192259757</v>
       </c>
       <c r="AK3">
-        <v>-0.006747638326585695</v>
+        <v>0.008490312635033342</v>
       </c>
       <c r="AL3">
         <v>0</v>
